--- a/business_forms/035_inspection_report_template--business_forms.xlsx
+++ b/business_forms/035_inspection_report_template--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Inspection Date</t>
+          <t>Inspection Date 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inspector details</t>
+          <t>Inspector Details 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Client details</t>
+          <t>Client Details 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'fair',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Fair', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Poor', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'inspector',_'label':_'inspector'}</t>
+          <t>inspector</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Inspector', 'label': 'Inspector'}</t>
+          <t>Inspector</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'manager',_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Manager', 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'supervisor',_'label':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Supervisor', 'label': 'Supervisor'}</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
